--- a/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:45:11+00:00</t>
+    <t>2025-07-08T14:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -396,7 +396,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-Country</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-Country|3.0.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -781,7 +781,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T14:52:18+00:00</t>
+    <t>2025-07-10T12:55:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
